--- a/output/北塩原村_第2次算定_個別台帳.xlsx
+++ b/output/北塩原村_第2次算定_個別台帳.xlsx
@@ -638,7 +638,7 @@
     <row r="15" ht="110" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>シートの構成。01_利用者台帳が記入する様式です（1人1行）。02_列の説明に、欄ごとの記入のしかたと、なぜその欄が要るかを書いています。03_見込量への集計は、台帳から計画書の表へ数える手順です。04_未充足と中断の記録は、受けられなかった支援を記録する様式です。05_照会との対応に、この台帳でまとめられる照会の一覧を載せています。この台帳をいただければ、Ｍ-15・Ｍ-20・Ｍ-21・Ｍ-22・Ｍ-23・Ｍ-24・Ｍ-85・Ｍ-87・Ｍ-89・Ｍ-90・Ｍ-91・Ｍ-92・Ｍ-93・Ｍ-94・Ｍ-106の回答に代えられます。</t>
+          <t>シートの構成。01_利用者台帳が記入する様式です（1人1行）。02_列の説明に、欄ごとの記入のしかたと、なぜその欄が要るかを書いています。03_見込量への集計は、台帳から計画書の表へ数える手順です。04_未充足と中断の記録は、受けられなかった支援を記録する様式です。05_照会との対応に、この台帳でまとめられる照会の一覧を載せています。この台帳をいただければ、Ｍ-15・Ｍ-20・Ｍ-21・Ｍ-22・Ｍ-24・Ｍ-85・Ｍ-87・Ｍ-89・Ｍ-90・Ｍ-91・Ｍ-92・Ｍ-93・Ｍ-94・Ｍ-106の回答に代えられます。</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Ｍ-23</t>
+          <t>Ｍ-109</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -3505,7 +3505,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Ｍ-23</t>
+          <t>Ｍ-109</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">

--- a/output/北塩原村_第2次算定_個別台帳.xlsx
+++ b/output/北塩原村_第2次算定_個別台帳.xlsx
@@ -658,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG24"/>
+  <dimension ref="A1:AJ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -673,27 +673,30 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="26" customWidth="1" min="16" max="16"/>
     <col width="26" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
     <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="18" customWidth="1" min="25" max="25"/>
-    <col width="18" customWidth="1" min="26" max="26"/>
-    <col width="18" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
-    <col width="16" customWidth="1" min="30" max="30"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="18" customWidth="1" min="29" max="29"/>
+    <col width="18" customWidth="1" min="30" max="30"/>
     <col width="16" customWidth="1" min="31" max="31"/>
     <col width="16" customWidth="1" min="32" max="32"/>
-    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
+    <col width="16" customWidth="1" min="35" max="35"/>
+    <col width="18" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -731,43 +734,46 @@
       <c r="J3" s="7" t="n"/>
       <c r="K3" s="7" t="n"/>
       <c r="L3" s="7" t="n"/>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="M3" s="7" t="n"/>
+      <c r="N3" s="7" t="n"/>
+      <c r="O3" s="6" t="inlineStr">
         <is>
           <t>本人の意思</t>
         </is>
       </c>
-      <c r="N3" s="7" t="n"/>
-      <c r="O3" s="7" t="n"/>
       <c r="P3" s="7" t="n"/>
       <c r="Q3" s="7" t="n"/>
       <c r="R3" s="7" t="n"/>
-      <c r="S3" s="6" t="inlineStr">
+      <c r="S3" s="7" t="n"/>
+      <c r="T3" s="7" t="n"/>
+      <c r="U3" s="6" t="inlineStr">
         <is>
           <t>年齢の到達</t>
         </is>
       </c>
-      <c r="T3" s="7" t="n"/>
-      <c r="U3" s="7" t="n"/>
       <c r="V3" s="7" t="n"/>
       <c r="W3" s="7" t="n"/>
       <c r="X3" s="7" t="n"/>
-      <c r="Y3" s="6" t="inlineStr">
-        <is>
-          <t>必要量</t>
-        </is>
-      </c>
+      <c r="Y3" s="7" t="n"/>
       <c r="Z3" s="7" t="n"/>
       <c r="AA3" s="7" t="n"/>
-      <c r="AB3" s="7" t="n"/>
-      <c r="AC3" s="6" t="inlineStr">
-        <is>
-          <t>確保と制約</t>
-        </is>
-      </c>
+      <c r="AB3" s="6" t="inlineStr">
+        <is>
+          <t>必要量</t>
+        </is>
+      </c>
+      <c r="AC3" s="7" t="n"/>
       <c r="AD3" s="7" t="n"/>
       <c r="AE3" s="7" t="n"/>
-      <c r="AF3" s="7" t="n"/>
+      <c r="AF3" s="6" t="inlineStr">
+        <is>
+          <t>確保と制約</t>
+        </is>
+      </c>
       <c r="AG3" s="7" t="n"/>
+      <c r="AH3" s="7" t="n"/>
+      <c r="AI3" s="7" t="n"/>
+      <c r="AJ3" s="7" t="n"/>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -822,115 +828,130 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
+          <t>必要があるが利用に至っていない支援</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>計画相談支援のモニタリングの期間</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
           <t>事業所の所在</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>事業所の指定の形</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>本人の意思</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>選好</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>価値観</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>意思の確かめ方</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>体験の利用</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>家族の意向</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>18歳到達年度</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>22歳到達年度</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>40歳到達年度</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>65歳到達年度</t>
         </is>
       </c>
-      <c r="V4" s="3" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>介護保険の認定</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>相当する介護保険サービス</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>同じ事業所で続けられるか</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>令和９年度の必要量</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>令和10年度の必要量</t>
         </is>
       </c>
-      <c r="AA4" s="3" t="inlineStr">
+      <c r="AD4" s="3" t="inlineStr">
         <is>
           <t>令和11年度の必要量</t>
         </is>
       </c>
-      <c r="AB4" s="3" t="inlineStr">
+      <c r="AE4" s="3" t="inlineStr">
         <is>
           <t>増減の理由</t>
         </is>
       </c>
-      <c r="AC4" s="3" t="inlineStr">
+      <c r="AF4" s="3" t="inlineStr">
         <is>
           <t>確保の見込み</t>
         </is>
       </c>
-      <c r="AD4" s="3" t="inlineStr">
+      <c r="AG4" s="3" t="inlineStr">
         <is>
           <t>送迎</t>
         </is>
       </c>
-      <c r="AE4" s="3" t="inlineStr">
+      <c r="AH4" s="3" t="inlineStr">
         <is>
           <t>冬季の通所</t>
         </is>
       </c>
-      <c r="AF4" s="3" t="inlineStr">
+      <c r="AI4" s="3" t="inlineStr">
         <is>
           <t>未充足として記録するもの</t>
         </is>
       </c>
-      <c r="AG4" s="3" t="inlineStr">
+      <c r="AJ4" s="3" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -970,6 +991,9 @@
       <c r="AE5" s="8" t="n"/>
       <c r="AF5" s="8" t="n"/>
       <c r="AG5" s="8" t="n"/>
+      <c r="AH5" s="8" t="n"/>
+      <c r="AI5" s="8" t="n"/>
+      <c r="AJ5" s="8" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="8" t="n"/>
@@ -1005,6 +1029,9 @@
       <c r="AE6" s="8" t="n"/>
       <c r="AF6" s="8" t="n"/>
       <c r="AG6" s="8" t="n"/>
+      <c r="AH6" s="8" t="n"/>
+      <c r="AI6" s="8" t="n"/>
+      <c r="AJ6" s="8" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="8" t="n"/>
@@ -1040,6 +1067,9 @@
       <c r="AE7" s="8" t="n"/>
       <c r="AF7" s="8" t="n"/>
       <c r="AG7" s="8" t="n"/>
+      <c r="AH7" s="8" t="n"/>
+      <c r="AI7" s="8" t="n"/>
+      <c r="AJ7" s="8" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="8" t="n"/>
@@ -1075,6 +1105,9 @@
       <c r="AE8" s="8" t="n"/>
       <c r="AF8" s="8" t="n"/>
       <c r="AG8" s="8" t="n"/>
+      <c r="AH8" s="8" t="n"/>
+      <c r="AI8" s="8" t="n"/>
+      <c r="AJ8" s="8" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="8" t="n"/>
@@ -1110,6 +1143,9 @@
       <c r="AE9" s="8" t="n"/>
       <c r="AF9" s="8" t="n"/>
       <c r="AG9" s="8" t="n"/>
+      <c r="AH9" s="8" t="n"/>
+      <c r="AI9" s="8" t="n"/>
+      <c r="AJ9" s="8" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="8" t="n"/>
@@ -1145,6 +1181,9 @@
       <c r="AE10" s="8" t="n"/>
       <c r="AF10" s="8" t="n"/>
       <c r="AG10" s="8" t="n"/>
+      <c r="AH10" s="8" t="n"/>
+      <c r="AI10" s="8" t="n"/>
+      <c r="AJ10" s="8" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="8" t="n"/>
@@ -1180,6 +1219,9 @@
       <c r="AE11" s="8" t="n"/>
       <c r="AF11" s="8" t="n"/>
       <c r="AG11" s="8" t="n"/>
+      <c r="AH11" s="8" t="n"/>
+      <c r="AI11" s="8" t="n"/>
+      <c r="AJ11" s="8" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="8" t="n"/>
@@ -1215,6 +1257,9 @@
       <c r="AE12" s="8" t="n"/>
       <c r="AF12" s="8" t="n"/>
       <c r="AG12" s="8" t="n"/>
+      <c r="AH12" s="8" t="n"/>
+      <c r="AI12" s="8" t="n"/>
+      <c r="AJ12" s="8" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="8" t="n"/>
@@ -1250,6 +1295,9 @@
       <c r="AE13" s="8" t="n"/>
       <c r="AF13" s="8" t="n"/>
       <c r="AG13" s="8" t="n"/>
+      <c r="AH13" s="8" t="n"/>
+      <c r="AI13" s="8" t="n"/>
+      <c r="AJ13" s="8" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="8" t="n"/>
@@ -1285,6 +1333,9 @@
       <c r="AE14" s="8" t="n"/>
       <c r="AF14" s="8" t="n"/>
       <c r="AG14" s="8" t="n"/>
+      <c r="AH14" s="8" t="n"/>
+      <c r="AI14" s="8" t="n"/>
+      <c r="AJ14" s="8" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="8" t="n"/>
@@ -1320,6 +1371,9 @@
       <c r="AE15" s="8" t="n"/>
       <c r="AF15" s="8" t="n"/>
       <c r="AG15" s="8" t="n"/>
+      <c r="AH15" s="8" t="n"/>
+      <c r="AI15" s="8" t="n"/>
+      <c r="AJ15" s="8" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="8" t="n"/>
@@ -1355,6 +1409,9 @@
       <c r="AE16" s="8" t="n"/>
       <c r="AF16" s="8" t="n"/>
       <c r="AG16" s="8" t="n"/>
+      <c r="AH16" s="8" t="n"/>
+      <c r="AI16" s="8" t="n"/>
+      <c r="AJ16" s="8" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="8" t="n"/>
@@ -1390,6 +1447,9 @@
       <c r="AE17" s="8" t="n"/>
       <c r="AF17" s="8" t="n"/>
       <c r="AG17" s="8" t="n"/>
+      <c r="AH17" s="8" t="n"/>
+      <c r="AI17" s="8" t="n"/>
+      <c r="AJ17" s="8" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="8" t="n"/>
@@ -1425,6 +1485,9 @@
       <c r="AE18" s="8" t="n"/>
       <c r="AF18" s="8" t="n"/>
       <c r="AG18" s="8" t="n"/>
+      <c r="AH18" s="8" t="n"/>
+      <c r="AI18" s="8" t="n"/>
+      <c r="AJ18" s="8" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="8" t="n"/>
@@ -1460,6 +1523,9 @@
       <c r="AE19" s="8" t="n"/>
       <c r="AF19" s="8" t="n"/>
       <c r="AG19" s="8" t="n"/>
+      <c r="AH19" s="8" t="n"/>
+      <c r="AI19" s="8" t="n"/>
+      <c r="AJ19" s="8" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="8" t="n"/>
@@ -1495,6 +1561,9 @@
       <c r="AE20" s="8" t="n"/>
       <c r="AF20" s="8" t="n"/>
       <c r="AG20" s="8" t="n"/>
+      <c r="AH20" s="8" t="n"/>
+      <c r="AI20" s="8" t="n"/>
+      <c r="AJ20" s="8" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="8" t="n"/>
@@ -1530,6 +1599,9 @@
       <c r="AE21" s="8" t="n"/>
       <c r="AF21" s="8" t="n"/>
       <c r="AG21" s="8" t="n"/>
+      <c r="AH21" s="8" t="n"/>
+      <c r="AI21" s="8" t="n"/>
+      <c r="AJ21" s="8" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="8" t="n"/>
@@ -1565,6 +1637,9 @@
       <c r="AE22" s="8" t="n"/>
       <c r="AF22" s="8" t="n"/>
       <c r="AG22" s="8" t="n"/>
+      <c r="AH22" s="8" t="n"/>
+      <c r="AI22" s="8" t="n"/>
+      <c r="AJ22" s="8" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="8" t="n"/>
@@ -1600,6 +1675,9 @@
       <c r="AE23" s="8" t="n"/>
       <c r="AF23" s="8" t="n"/>
       <c r="AG23" s="8" t="n"/>
+      <c r="AH23" s="8" t="n"/>
+      <c r="AI23" s="8" t="n"/>
+      <c r="AJ23" s="8" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="8" t="n"/>
@@ -1635,17 +1713,20 @@
       <c r="AE24" s="8" t="n"/>
       <c r="AF24" s="8" t="n"/>
       <c r="AG24" s="8" t="n"/>
+      <c r="AH24" s="8" t="n"/>
+      <c r="AI24" s="8" t="n"/>
+      <c r="AJ24" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A1:AG1"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="AC3:AG3"/>
+    <mergeCell ref="AF3:AJ3"/>
+    <mergeCell ref="AB3:AE3"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:AG2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="Y3:AB3"/>
-    <mergeCell ref="S3:X3"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="A2:AJ2"/>
+    <mergeCell ref="U3:AA3"/>
+    <mergeCell ref="O3:T3"/>
+    <mergeCell ref="A1:AJ1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1657,7 +1738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2098,32 +2179,32 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>事業所の所在</t>
+          <t>必要があるが利用に至っていない支援</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>村内又は市町村名。複数あれば併記</t>
+          <t>必要と考えられるが支給決定も利用もしていない支援の名称と量。無い場合は「該当なし」、分からない場合は「把握していない」</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>猪苗代町</t>
+          <t>短期入所（家族の休息のため）</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>村外の事業所に依存している度合いを確かめる。送迎と冬季の制約に直に効く</t>
+          <t>見込量の算式の起点を期首の必要者数に置くために要る。実際に利用している方だけを起点にすると、令和８年度に既に足りていない分がそのまま次の３年間にも足りないまま残る</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Ｍ-24</t>
+          <t>Ｍ-89・Ｍ-115</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>第5章2（4）広域連携によるサービス提供体制の確保</t>
+          <t>第5章1 表5-3 必要な利用者数の組み立て（起点）</t>
         </is>
       </c>
     </row>
@@ -2135,106 +2216,106 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>事業所の指定の形</t>
+          <t>計画相談支援のモニタリングの期間</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>通常の指定・共生型の指定・基準該当障害福祉サービスとしての取扱いのいずれか。分からない場合は「把握していない」</t>
+          <t>モニタリングを行う間隔（毎月・３月ごと・６月ごと・12月ごと等）。セルフプランの場合は「セルフプラン」、分からない場合は「把握していない」</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>通常の指定</t>
+          <t>３月ごと</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>65歳に達した後に同じ事業所で続けられるかが分かれる。共生型は指定の手続の特例であり、事業者の申請が要る</t>
+          <t>計画相談支援の見込量は人／月であり、相談支援専門員の負荷は年間の実施回数で決まる。のぞまないセルフプラン０件という成果目標が成り立つかを量で確かめるために要る</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-106</t>
+          <t>Ｍ-115</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>第5章5（2）表5-37 事業所の指定の形と65歳到達後の続け方</t>
+          <t>第5章1（4）相談支援・第4章2（6）相談支援体制の充実・強化等</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>本人の意思</t>
+          <t>いま受けている支援</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>本人の意思</t>
+          <t>事業所の所在</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>どのように暮らしたいか。本人の言葉をそのまま書く。支援者の見立ては書かない</t>
+          <t>村内又は市町村名。複数あれば併記</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>いまの通所を続けたい</t>
+          <t>猪苗代町</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第２版は、どのような障がいがあっても意思決定能力があることを前提とする</t>
+          <t>村外の事業所に依存している度合いを確かめる。送迎と冬季の制約に直に効く</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Ｍ-94</t>
+          <t>Ｍ-24</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>第4章2（7）意思決定支援・第4章2（1）地域生活への移行</t>
+          <t>第5章2（4）広域連携によるサービス提供体制の確保</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>本人の意思</t>
+          <t>いま受けている支援</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>選好</t>
+          <t>事業所の指定の形</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>好むこと・避けたいこと。場所、人、時間帯、過ごし方等</t>
+          <t>通常の指定・共生型の指定・基準該当障害福祉サービスとしての取扱いのいずれか。分からない場合は「把握していない」</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>人が多い場所は苦手</t>
+          <t>通常の指定</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>「本人の意思と選好に基づく最善の解釈」を行うための材料。本人が意思を示せない場面でも、選好は手がかりになる</t>
+          <t>65歳に達した後に同じ事業所で続けられるかが分かれる。共生型は指定の手続の特例であり、事業者の申請が要る</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-94</t>
+          <t>Ｍ-106</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>第5章5（2）表5-37 事業所の指定の形と65歳到達後の続け方</t>
         </is>
       </c>
     </row>
@@ -2246,22 +2327,22 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>価値観</t>
+          <t>本人の意思</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>大事にしていること。仕事、家族、役割、信仰、習慣等</t>
+          <t>どのように暮らしたいか。本人の言葉をそのまま書く。支援者の見立ては書かない</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>働くことを続けたい</t>
+          <t>いまの通所を続けたい</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>第２版が「意思、選好及び価値観」を一組として扱っている。価値観は時間が経っても変わりにくく、意思が確かめられない場面の支えになる</t>
+          <t>意思決定支援ガイドライン第２版は、どのような障がいがあっても意思決定能力があることを前提とする</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -2271,7 +2352,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>第4章2（7）意思決定支援・第4章2（1）地域生活への移行</t>
         </is>
       </c>
     </row>
@@ -2283,22 +2364,22 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>意思の確かめ方</t>
+          <t>選好</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>本人から直に聴いた・絵記号や写真を用いた・日頃の様子から読み取った・成年後見人等を通じた・未確認 の別</t>
+          <t>好むこと・避けたいこと。場所、人、時間帯、過ごし方等</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>本人から直に聴いた</t>
+          <t>人が多い場所は苦手</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>誰の意思なのかを後から追えるようにする。「未確認」をそのまま書けることが大事である</t>
+          <t>「本人の意思と選好に基づく最善の解釈」を行うための材料。本人が意思を示せない場面でも、選好は手がかりになる</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -2308,7 +2389,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>第4章2（7）意思決定支援</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
@@ -2320,22 +2401,22 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>体験の利用</t>
+          <t>価値観</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>共同生活援助・短期入所・日中活動の体験の有無と内容。体験していない場合は「していない」</t>
+          <t>大事にしていること。仕事、家族、役割、信仰、習慣等</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>していない</t>
+          <t>働くことを続けたい</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>経験していないことについての意思は形になりにくい。体験の機会を用意してから意向を確かめる</t>
+          <t>第２版が「意思、選好及び価値観」を一組として扱っている。価値観は時間が経っても変わりにくく、意思が確かめられない場面の支えになる</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -2345,7 +2426,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>第4章2（1）表4-4 地域移行の可能性を確かめる事項</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
@@ -2357,22 +2438,22 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>家族の意向</t>
+          <t>意思の確かめ方</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>家族の意向。本人の意思と一致しない場合は一致しない旨を書く</t>
+          <t>本人から直に聴いた・絵記号や写真を用いた・日頃の様子から読み取った・成年後見人等を通じた・未確認 の別</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>自宅での生活を続けてほしい</t>
+          <t>本人から直に聴いた</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>本人の意思と家族の意向は別である。同じ欄に書くと、どちらの意向かが分からなくなる</t>
+          <t>誰の意思なのかを後から追えるようにする。「未確認」をそのまま書けることが大事である</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2382,81 +2463,81 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>第4章2（1）表4-3・第5章5（1）学校卒業に伴う移行</t>
+          <t>第4章2（7）意思決定支援</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>年齢の到達</t>
+          <t>本人の意思</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>18歳到達年度</t>
+          <t>体験の利用</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>令和９〜11年度に18歳に達する場合はその年度。該当しない場合は「該当なし」</t>
+          <t>共同生活援助・短期入所・日中活動の体験の有無と内容。体験していない場合は「していない」</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>令和９年度</t>
+          <t>していない</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>障がい児支援から障がい福祉サービスへ移る。障がい児支援の減と障がい福祉サービスの増を対応させる</t>
+          <t>経験していないことについての意思は形になりにくい。体験の機会を用意してから意向を確かめる</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Ｍ-21</t>
+          <t>Ｍ-94</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>第5章5（1）18歳到達・学校卒業に伴う移行</t>
+          <t>第4章2（1）表4-4 地域移行の可能性を確かめる事項</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>年齢の到達</t>
+          <t>本人の意思</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>40歳到達年度</t>
+          <t>家族の意向</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>令和９〜11年度に40歳に達する場合はその年度。該当しない場合は「該当なし」</t>
+          <t>家族の意向。本人の意思と一致しない場合は一致しない旨を書く</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>該当なし</t>
+          <t>自宅での生活を続けてほしい</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>40歳以上65歳未満は、16の特定疾病に該当して要介護認定を受けると介護保険の第２号被保険者になる</t>
+          <t>本人の意思と家族の意向は別である。同じ欄に書くと、どちらの意向かが分からなくなる</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-14</t>
+          <t>Ｍ-94</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>第5章5（2）65歳到達時のサービスの区分</t>
+          <t>第4章2（1）表4-3・第5章5（1）学校卒業に伴う移行</t>
         </is>
       </c>
     </row>
@@ -2468,32 +2549,32 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>65歳到達年度</t>
+          <t>18歳到達年度</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>令和９〜11年度に65歳に達する場合はその年度。該当しない場合は「該当なし」</t>
+          <t>令和９〜11年度に18歳に達する場合はその年度。該当しない場合は「該当なし」</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>該当なし</t>
+          <t>令和９年度</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>介護保険優先原則の適用を個別に判定する時期を決める。概ね６か月前から進める</t>
+          <t>障がい児支援から障がい福祉サービスへ移る。障がい児支援の減と障がい福祉サービスの増を対応させる</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Ｍ-15・Ｍ-20</t>
+          <t>Ｍ-21</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>第5章5（2）表5-39 65歳到達時の引継ぎの時期と担当</t>
+          <t>第5章5（1）18歳到達・学校卒業に伴う移行</t>
         </is>
       </c>
     </row>
@@ -2505,32 +2586,32 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>介護保険の認定</t>
+          <t>22歳到達年度</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>認定なし・申請中・要支援１〜２・要介護１〜５ の別</t>
+          <t>障害児入所施設に入所している方で、令和９〜11年度に22歳に達する場合はその年度。該当しない場合は「該当なし」</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>認定なし</t>
+          <t>該当なし</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>認定がないまま介護保険優先原則を当てはめることはしない</t>
+          <t>改正児童福祉法（令和６年４月施行）により22歳満了までの入所継続ができる。満了に伴い成人のサービスへ移るため、その年度の流入として数える。移行調整の責任主体は県であるため、村が単独で数えず県・入所施設と確かめる</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-14</t>
+          <t>Ｍ-115</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>第5章5（2）表5-38 65歳到達時に確認する事項</t>
+          <t>第5章1 表5-3 必要な利用者数の組み立て</t>
         </is>
       </c>
     </row>
@@ -2542,32 +2623,32 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>相当する介護保険サービス</t>
+          <t>40歳到達年度</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>あり（サービス名）・なし の別。共同生活援助、施設入所支援、就労系、同行援護、行動援護は相当するものがない</t>
+          <t>令和９〜11年度に40歳に達する場合はその年度。該当しない場合は「該当なし」</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>該当なし</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>相当するものがなければ65歳到達後も障がい福祉サービスとして続く。一律に減じない根拠になる</t>
+          <t>40歳以上65歳未満は、16の特定疾病に該当して要介護認定を受けると介護保険の第２号被保険者になる</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>Ｍ-14</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>第5章5（2）表5-36 65歳到達時のサービスの区分</t>
+          <t>第5章5（2）65歳到達時のサービスの区分</t>
         </is>
       </c>
     </row>
@@ -2579,143 +2660,143 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>同じ事業所で続けられるか</t>
+          <t>65歳到達年度</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>続けられる・事業所が変わる・分からない の別。続けられる場合はその理由（共生型の指定等）</t>
+          <t>令和９〜11年度に65歳に達する場合はその年度。該当しない場合は「該当なし」</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>分からない</t>
+          <t>該当なし</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>国が共生型サービスを設けたねらいの一つは、65歳以上になっても使い慣れた事業所で利用しやすくすることにある。中断がなくても事業所が変われば本人にとっては大きい変化である</t>
+          <t>介護保険優先原則の適用を個別に判定する時期を決める。概ね６か月前から進める</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-106</t>
+          <t>Ｍ-15・Ｍ-20</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>第5章5（2）表5-37・12重点施策No.5の確認項目</t>
+          <t>第5章5（2）表5-39 65歳到達時の引継ぎの時期と担当</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>必要量</t>
+          <t>年齢の到達</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>令和９年度の必要量</t>
+          <t>介護保険の認定</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>サービスごとに、人数と量（人日・時間）。利用しない場合は「０」</t>
+          <t>認定なし・申請中・要支援１〜２・要介護１〜５ の別</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>22人日／月</t>
+          <t>認定なし</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>第2次算定の核になる欄。過去の実績の延長ではなく、本人ごとの必要量を積む</t>
+          <t>認定がないまま介護保険優先原則を当てはめることはしない</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Ｍ-87〜Ｍ-94</t>
+          <t>Ｍ-14</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>第5章1 表5-5・表5-8・表5-11・表5-13・表5-15</t>
+          <t>第5章5（2）表5-38 65歳到達時に確認する事項</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>必要量</t>
+          <t>年齢の到達</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>令和10年度の必要量</t>
+          <t>相当する介護保険サービス</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>同じ形で記入</t>
+          <t>あり（サービス名）・なし の別。共同生活援助、施設入所支援、就労系、同行援護、行動援護は相当するものがない</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>22人日／月</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>相当するものがなければ65歳到達後も障がい福祉サービスとして続く。一律に減じない根拠になる</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-87〜Ｍ-94</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>第5章5（2）表5-36 65歳到達時のサービスの区分</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>必要量</t>
+          <t>年齢の到達</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>令和11年度の必要量</t>
+          <t>同じ事業所で続けられるか</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>同じ形で記入</t>
+          <t>続けられる・事業所が変わる・分からない の別。続けられる場合はその理由（共生型の指定等）</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>22人日／月</t>
+          <t>分からない</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>国が共生型サービスを設けたねらいの一つは、65歳以上になっても使い慣れた事業所で利用しやすくすることにある。中断がなくても事業所が変われば本人にとっては大きい変化である</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Ｍ-87〜Ｍ-94</t>
+          <t>Ｍ-106</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>第5章5（2）表5-37・12重点施策No.5の確認項目</t>
         </is>
       </c>
     </row>
@@ -2727,143 +2808,143 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>増減の理由</t>
+          <t>令和９年度の必要量</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>増える場合・減る場合の理由。18歳到達、卒業、地域移行、一般就労、65歳到達、転出等</t>
+          <t>サービスごとに、人数と量（人日・時間）。利用しない場合は「０」</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>卒業に伴い新たに利用</t>
+          <t>22人日／月</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>数の動きに理由が付いていないと、次の計画で評価できない</t>
+          <t>第2次算定の核になる欄。過去の実績の延長ではなく、本人ごとの必要量を積む</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>Ｍ-87〜Ｍ-94</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>第5章1 表5-3 必要な利用者数の組み立て</t>
+          <t>第5章1 表5-5・表5-8・表5-11・表5-13・表5-15</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>確保と制約</t>
+          <t>必要量</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>確保の見込み</t>
+          <t>令和10年度の必要量</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>村内で確保・圏域で確保・確保できない の別</t>
+          <t>同じ形で記入</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>圏域で確保</t>
+          <t>22人日／月</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>必要量と確保できる量を分けて把握する。確保できない分が未充足量になる</t>
+          <t>同上</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Ｍ-24</t>
+          <t>Ｍ-87〜Ｍ-94</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>第5章2 必要な見込量の確保のための方策</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>確保と制約</t>
+          <t>必要量</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>送迎</t>
+          <t>令和11年度の必要量</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>事業所の送迎あり（範囲）・家族の送迎・公共交通・移動支援 の別</t>
+          <t>同じ形で記入</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>事業所の送迎あり（村内まで）</t>
+          <t>22人日／月</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>送迎がなければ、事業所があっても通えない</t>
+          <t>同上</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-24</t>
+          <t>Ｍ-87〜Ｍ-94</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>第5章2（4）通所に係る移動手段の確保</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>確保と制約</t>
+          <t>必要量</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>冬季の通所</t>
+          <t>増減の理由</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>通える・通えない日がある・分からない の別。通えない日がある場合は年間の日数の目安</t>
+          <t>増える場合・減る場合の理由。18歳到達、卒業、地域移行、一般就労、65歳到達、転出等</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>通えない日がある（年５日程度）</t>
+          <t>卒業に伴い新たに利用</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>本村では冬季が最も重い制約になる。中断した日数を記録しないと、必要量を満たしたかどうかが分からない</t>
+          <t>数の動きに理由が付いていないと、次の計画で評価できない</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Ｍ-85</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>第5章2（12）冬季の支援</t>
+          <t>第5章1 表5-3 必要な利用者数の組み立て</t>
         </is>
       </c>
     </row>
@@ -2875,32 +2956,32 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>未充足として記録するもの</t>
+          <t>確保の見込み</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>受けられなかった支援とその理由。無い場合は「該当なし」</t>
+          <t>村内で確保・圏域で確保・確保できない の別</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>該当なし</t>
+          <t>圏域で確保</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>確保できない分は圏域での確保又は未充足として記録する。記録しなければ次の計画に引き継げない</t>
+          <t>必要量と確保できる量を分けて把握する。確保できない分が未充足量になる</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>Ｍ-24</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>第5章2 必要な見込量の確保のための方策・第1章6 点検評価</t>
+          <t>第5章2 必要な見込量の確保のための方策</t>
         </is>
       </c>
     </row>
@@ -2912,30 +2993,141 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
+          <t>送迎</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>事業所の送迎あり（範囲）・家族の送迎・公共交通・移動支援 の別</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>事業所の送迎あり（村内まで）</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>送迎がなければ、事業所があっても通えない</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Ｍ-24</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>第5章2（4）通所に係る移動手段の確保</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>確保と制約</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>冬季の通所</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>通える・通えない日がある・分からない の別。通えない日がある場合は年間の日数の目安</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>通えない日がある（年５日程度）</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>本村では冬季が最も重い制約になる。中断した日数を記録しないと、必要量を満たしたかどうかが分からない</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Ｍ-85</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>第5章2（12）冬季の支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>確保と制約</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>未充足として記録するもの</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>受けられなかった支援とその理由。無い場合は「該当なし」</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>該当なし</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>確保できない分は圏域での確保又は未充足として記録する。記録しなければ次の計画に引き継げない</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>第5章2 必要な見込量の確保のための方策・第1章6 点検評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>確保と制約</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>上の欄に収まらないこと。継続入所者に当たる場合はその旨</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>継続入所者（整備法前の指定知的障害児施設等からの引き続きの入所）は、施設入所支援の見込量から除く</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>Ｍ-109</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>第5章1（3）居住系サービス</t>
         </is>

--- a/output/北塩原村_第2次算定_個別台帳.xlsx
+++ b/output/北塩原村_第2次算定_個別台帳.xlsx
@@ -1982,7 +1982,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>第5章1（2）強度行動障害を有する方等の生活介護の利用の見込み</t>
+          <t>第5章1（2）強度行動障害を有する方等の重度障がい者の内数の見込み</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>表５-９　強度行動障害を有する方等の生活介護の利用の見込み</t>
+          <t>表５-９　強度行動障害を有する方等の重度障がい者の内数の見込み</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
